--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A4E34A-C548-48E4-BAA3-13750B035B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2CF1B9-995A-4D14-8002-52D89F1DAE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Zainab</t>
   </si>
   <si>
-    <t>01/01/1964</t>
+    <t>01/01/1964 00:00:00</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
+    <t>19/09/2024 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/1900 00:00:00</t>
   </si>
   <si>
     <t>AHMED</t>
@@ -91,10 +91,10 @@
     <t>Monira</t>
   </si>
   <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
+    <t>01/01/1987 00:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2025 00:00:00</t>
   </si>
   <si>
     <t>MPUTU</t>
@@ -103,13 +103,13 @@
     <t>Bella</t>
   </si>
   <si>
-    <t>20/05/1998</t>
+    <t>20/05/1998 00:00:00</t>
   </si>
   <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>04/11/2025</t>
+    <t>04/11/2025 00:00:00</t>
   </si>
   <si>
     <t>PETROSYAN</t>
@@ -118,13 +118,13 @@
     <t>Anna</t>
   </si>
   <si>
-    <t>07/10/1992</t>
+    <t>07/10/1992 00:00:00</t>
   </si>
   <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>20/03/2025</t>
+    <t>20/03/2025 00:00:00</t>
   </si>
   <si>
     <t>POGHOSYAN</t>
@@ -133,10 +133,10 @@
     <t>Gayane</t>
   </si>
   <si>
-    <t>25/09/1960</t>
-  </si>
-  <si>
-    <t>27/09/2023</t>
+    <t>25/09/1960 00:00:00</t>
+  </si>
+  <si>
+    <t>27/09/2023 00:00:00</t>
   </si>
   <si>
     <t>SAYED</t>
@@ -145,19 +145,19 @@
     <t>Mohammad</t>
   </si>
   <si>
-    <t>05/08/1989</t>
+    <t>05/08/1989 00:00:00</t>
   </si>
   <si>
     <t>Allemagne</t>
   </si>
   <si>
-    <t>16/09/2025</t>
+    <t>16/09/2025 00:00:00</t>
   </si>
   <si>
     <t>Tamara</t>
   </si>
   <si>
-    <t>24/07/1985</t>
+    <t>24/07/1985 00:00:00</t>
   </si>
   <si>
     <t>YELEJYAN</t>
@@ -166,10 +166,10 @@
     <t>Gohar</t>
   </si>
   <si>
-    <t>20/12/1983</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
+    <t>20/12/1983 00:00:00</t>
+  </si>
+  <si>
+    <t>03/09/2025 00:00:00</t>
   </si>
 </sst>
 </file>
@@ -656,7 +656,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2CF1B9-995A-4D14-8002-52D89F1DAE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4990C4F-3BAA-4331-AD3C-A0A06344BED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Zainab</t>
   </si>
   <si>
-    <t>01/01/1964 00:00:00</t>
+    <t>01/01/1964</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>19/09/2024 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/1900 00:00:00</t>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
   </si>
   <si>
     <t>AHMED</t>
@@ -91,10 +91,10 @@
     <t>Monira</t>
   </si>
   <si>
-    <t>01/01/1987 00:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2025 00:00:00</t>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
   </si>
   <si>
     <t>MPUTU</t>
@@ -103,13 +103,13 @@
     <t>Bella</t>
   </si>
   <si>
-    <t>20/05/1998 00:00:00</t>
+    <t>20/05/1998</t>
   </si>
   <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>04/11/2025 00:00:00</t>
+    <t>04/11/2025</t>
   </si>
   <si>
     <t>PETROSYAN</t>
@@ -118,13 +118,13 @@
     <t>Anna</t>
   </si>
   <si>
-    <t>07/10/1992 00:00:00</t>
+    <t>07/10/1992</t>
   </si>
   <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>20/03/2025 00:00:00</t>
+    <t>20/03/2025</t>
   </si>
   <si>
     <t>POGHOSYAN</t>
@@ -133,10 +133,10 @@
     <t>Gayane</t>
   </si>
   <si>
-    <t>25/09/1960 00:00:00</t>
-  </si>
-  <si>
-    <t>27/09/2023 00:00:00</t>
+    <t>25/09/1960</t>
+  </si>
+  <si>
+    <t>27/09/2023</t>
   </si>
   <si>
     <t>SAYED</t>
@@ -145,19 +145,19 @@
     <t>Mohammad</t>
   </si>
   <si>
-    <t>05/08/1989 00:00:00</t>
+    <t>05/08/1989</t>
   </si>
   <si>
     <t>Allemagne</t>
   </si>
   <si>
-    <t>16/09/2025 00:00:00</t>
+    <t>16/09/2025</t>
   </si>
   <si>
     <t>Tamara</t>
   </si>
   <si>
-    <t>24/07/1985 00:00:00</t>
+    <t>24/07/1985</t>
   </si>
   <si>
     <t>YELEJYAN</t>
@@ -166,10 +166,10 @@
     <t>Gohar</t>
   </si>
   <si>
-    <t>20/12/1983 00:00:00</t>
-  </si>
-  <si>
-    <t>03/09/2025 00:00:00</t>
+    <t>20/12/1983</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
   </si>
 </sst>
 </file>
@@ -656,7 +656,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4990C4F-3BAA-4331-AD3C-A0A06344BED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC74539-3E18-42EB-AC96-9D3FF25B8EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC74539-3E18-42EB-AC96-9D3FF25B8EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509A7E69-2808-4674-A0A2-3404097AEC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,66 +52,27 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
-    <t>ABDALLA MIRGHANI</t>
-  </si>
-  <si>
-    <t>Zainab</t>
-  </si>
-  <si>
-    <t>01/01/1964</t>
-  </si>
-  <si>
-    <t>Soudan</t>
+    <t>MPUTU</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>20/05/1998</t>
+  </si>
+  <si>
+    <t>République démocratique du Congo</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>19/09/2024</t>
+    <t>04/11/2025</t>
   </si>
   <si>
     <t>01/01/1900</t>
   </si>
   <si>
-    <t>AHMED</t>
-  </si>
-  <si>
-    <t>Ibrahim</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>AHMED MOHAMED OSMAN</t>
-  </si>
-  <si>
-    <t>Monira</t>
-  </si>
-  <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>MPUTU</t>
-  </si>
-  <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>20/05/1998</t>
-  </si>
-  <si>
-    <t>République démocratique du Congo</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
     <t>PETROSYAN</t>
   </si>
   <si>
@@ -125,39 +86,6 @@
   </si>
   <si>
     <t>20/03/2025</t>
-  </si>
-  <si>
-    <t>POGHOSYAN</t>
-  </si>
-  <si>
-    <t>Gayane</t>
-  </si>
-  <si>
-    <t>25/09/1960</t>
-  </si>
-  <si>
-    <t>27/09/2023</t>
-  </si>
-  <si>
-    <t>SAYED</t>
-  </si>
-  <si>
-    <t>Mohammad</t>
-  </si>
-  <si>
-    <t>05/08/1989</t>
-  </si>
-  <si>
-    <t>Allemagne</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
-    <t>Tamara</t>
-  </si>
-  <si>
-    <t>24/07/1985</t>
   </si>
   <si>
     <t>YELEJYAN</t>
@@ -744,16 +672,16 @@
         <v>17</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
@@ -764,182 +692,98 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="6">

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509A7E69-2808-4674-A0A2-3404097AEC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169C8FBD-3FCB-4100-8D3A-17488B2D62DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169C8FBD-3FCB-4100-8D3A-17488B2D62DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F48D9D6-E57E-4EC6-A286-921CF2FBD9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F48D9D6-E57E-4EC6-A286-921CF2FBD9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CF9F27-3017-4DA8-8E50-DDF9901EECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CF9F27-3017-4DA8-8E50-DDF9901EECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1D3E80-7205-43AB-A4CB-D703E4BCCD08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,6 +52,51 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
+    <t>ABDALLA MIRGHANI</t>
+  </si>
+  <si>
+    <t>Zainab</t>
+  </si>
+  <si>
+    <t>01/01/1964</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>AHMED</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>AHMED MOHAMED OSMAN</t>
+  </si>
+  <si>
+    <t>Monira</t>
+  </si>
+  <si>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
     <t>MPUTU</t>
   </si>
   <si>
@@ -64,15 +109,9 @@
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>04/11/2025</t>
   </si>
   <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>PETROSYAN</t>
   </si>
   <si>
@@ -86,6 +125,39 @@
   </si>
   <si>
     <t>20/03/2025</t>
+  </si>
+  <si>
+    <t>POGHOSYAN</t>
+  </si>
+  <si>
+    <t>Gayane</t>
+  </si>
+  <si>
+    <t>25/09/1960</t>
+  </si>
+  <si>
+    <t>27/09/2023</t>
+  </si>
+  <si>
+    <t>SAYED</t>
+  </si>
+  <si>
+    <t>Mohammad</t>
+  </si>
+  <si>
+    <t>05/08/1989</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
+    <t>Tamara</t>
+  </si>
+  <si>
+    <t>24/07/1985</t>
   </si>
   <si>
     <t>YELEJYAN</t>
@@ -672,16 +744,16 @@
         <v>17</v>
       </c>
       <c r="D5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>13</v>
-      </c>
       <c r="G5" s="13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
@@ -692,98 +764,182 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="3"/>
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="3"/>
+      <c r="B8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>6</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="3"/>
+      <c r="B9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="3"/>
+      <c r="B10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="3"/>
+      <c r="B11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="3"/>
+      <c r="B12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="6">
